--- a/wiki/di/BradescoRSM.xlsx
+++ b/wiki/di/BradescoRSM.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enrique.escobar\Disk_X\bbank_dw\wiki\di\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{485AED90-AA69-4637-95D6-BD8A363C0563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C5CD1F-5980-48BB-8583-5B891EC38BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2E3D8C18-206E-4258-BE0B-F3DC62B20D77}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" activeTab="2" xr2:uid="{2E3D8C18-206E-4258-BE0B-F3DC62B20D77}"/>
   </bookViews>
   <sheets>
-    <sheet name="WBSdetail" sheetId="1" r:id="rId1"/>
-    <sheet name="Metrics" sheetId="2" r:id="rId2"/>
+    <sheet name="Metrics" sheetId="2" r:id="rId1"/>
+    <sheet name="WBSdetail" sheetId="1" r:id="rId2"/>
+    <sheet name="WBS" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="330">
   <si>
     <t>WBS ID</t>
   </si>
@@ -688,6 +689,345 @@
   </si>
   <si>
     <t>Overall Program Completion Estimate</t>
+  </si>
+  <si>
+    <t>1_Project Governance &amp; Engagement Management</t>
+  </si>
+  <si>
+    <t>1.1_Project Initiation</t>
+  </si>
+  <si>
+    <t>1.1.1_Kickoff Meeting</t>
+  </si>
+  <si>
+    <t>1.1.2_Stakeholder Register</t>
+  </si>
+  <si>
+    <t>1.1.3_Assessment Methodology</t>
+  </si>
+  <si>
+    <t>1.1.4_Communication Plan</t>
+  </si>
+  <si>
+    <t>2_Current State Data Governance Assessment</t>
+  </si>
+  <si>
+    <t>2.1_Governance Operating Model Assessment</t>
+  </si>
+  <si>
+    <t>2.1.1_Executive Sponsorship Assessment</t>
+  </si>
+  <si>
+    <t>2.1.2_Decision Rights Assessment</t>
+  </si>
+  <si>
+    <t>2.1.3_Stewardship Assessment</t>
+  </si>
+  <si>
+    <t>2.1.4_Ownership Assessment</t>
+  </si>
+  <si>
+    <t>2.2_Data Domain Assessment</t>
+  </si>
+  <si>
+    <t>2.2.1_Customer Domain</t>
+  </si>
+  <si>
+    <t>2.2.2_Deposit Domain</t>
+  </si>
+  <si>
+    <t>2.2.3_Time Deposit Domain</t>
+  </si>
+  <si>
+    <t>2.2.4_Treasury Domain</t>
+  </si>
+  <si>
+    <t>2.2.5_Finance Domain</t>
+  </si>
+  <si>
+    <t>2.2.6_Regulatory Reporting Domain</t>
+  </si>
+  <si>
+    <t>2.2.7_Risk Domain</t>
+  </si>
+  <si>
+    <t>2.3_Data Asset Assessment</t>
+  </si>
+  <si>
+    <t>2.3.1_Source System Inventory</t>
+  </si>
+  <si>
+    <t>2.3.2_Product Inventory Review</t>
+  </si>
+  <si>
+    <t>2.3.3_Business Glossary Seed</t>
+  </si>
+  <si>
+    <t>3_Metadata &amp; Catalog Assessment</t>
+  </si>
+  <si>
+    <t>3.1_Business Metadata Assessment</t>
+  </si>
+  <si>
+    <t>3.1.1_Glossary Assessment</t>
+  </si>
+  <si>
+    <t>3.1.2_Definition Standardization</t>
+  </si>
+  <si>
+    <t>3.2_Technical Metadata Assessment</t>
+  </si>
+  <si>
+    <t>3.2.1_Catalog Coverage Assessment</t>
+  </si>
+  <si>
+    <t>4_Data Lineage Assessment</t>
+  </si>
+  <si>
+    <t>4.1_Enterprise Lineage Review</t>
+  </si>
+  <si>
+    <t>4.1.1_Source-to-Landing Review</t>
+  </si>
+  <si>
+    <t>4.1.2_Landing-to-Warehouse Review</t>
+  </si>
+  <si>
+    <t>4.1.3_Warehouse-to-Reporting Review</t>
+  </si>
+  <si>
+    <t>4.1.4_Regulatory Traceability Review</t>
+  </si>
+  <si>
+    <t>5_Data Quality Assessment</t>
+  </si>
+  <si>
+    <t>5.1_Data Quality Framework Review</t>
+  </si>
+  <si>
+    <t>5.1.1_Completeness Assessment</t>
+  </si>
+  <si>
+    <t>5.1.2_Accuracy Assessment</t>
+  </si>
+  <si>
+    <t>5.1.3_Consistency Assessment</t>
+  </si>
+  <si>
+    <t>5.1.4_Timeliness Assessment</t>
+  </si>
+  <si>
+    <t>5.1.5_Validity Assessment</t>
+  </si>
+  <si>
+    <t>5.2_Critical Data Elements Program</t>
+  </si>
+  <si>
+    <t>5.2.1_CDE Inventory</t>
+  </si>
+  <si>
+    <t>5.2.2_CDE Ownership</t>
+  </si>
+  <si>
+    <t>5.2.3_CDE Rule Definition</t>
+  </si>
+  <si>
+    <t>6_SecurityPrivacy_AndComplianceAssessment</t>
+  </si>
+  <si>
+    <t>6.1_Data Classification Assessment</t>
+  </si>
+  <si>
+    <t>6.1.1_Public Classification Review</t>
+  </si>
+  <si>
+    <t>6.1.2_Internal Classification Review</t>
+  </si>
+  <si>
+    <t>6.1.3_Confidential Classification Review</t>
+  </si>
+  <si>
+    <t>6.1.4_Restricted Classification Review</t>
+  </si>
+  <si>
+    <t>6.2_Regulatory Controls Assessment</t>
+  </si>
+  <si>
+    <t>6.1.1_TBD</t>
+  </si>
+  <si>
+    <t>7_Current State Maturity Assessment</t>
+  </si>
+  <si>
+    <t>7.1_Strategy &amp; Vision</t>
+  </si>
+  <si>
+    <t>7.1.1_TBD</t>
+  </si>
+  <si>
+    <t>7.2_Policies &amp; Standards</t>
+  </si>
+  <si>
+    <t>7.2.1_TBD</t>
+  </si>
+  <si>
+    <t>7.3_Organization &amp; Roles</t>
+  </si>
+  <si>
+    <t>7.3.1_TBD</t>
+  </si>
+  <si>
+    <t>7.4_Metadata &amp; Catalog</t>
+  </si>
+  <si>
+    <t>7.4.1_TBD</t>
+  </si>
+  <si>
+    <t>7.5_Data Lineage</t>
+  </si>
+  <si>
+    <t>7.5.1_TBD</t>
+  </si>
+  <si>
+    <t>7.6_Data Quality</t>
+  </si>
+  <si>
+    <t>7.6.1_TBD</t>
+  </si>
+  <si>
+    <t>7.7_Classification &amp; Privacy</t>
+  </si>
+  <si>
+    <t>7.7.1_TBD</t>
+  </si>
+  <si>
+    <t>7.8_Retention &amp; Records</t>
+  </si>
+  <si>
+    <t>7.8.1_TBD</t>
+  </si>
+  <si>
+    <t>7.9_Architecture &amp; Platform</t>
+  </si>
+  <si>
+    <t>7.9.1_TBD</t>
+  </si>
+  <si>
+    <t>7.10_Monitoring &amp; Reporting</t>
+  </si>
+  <si>
+    <t>7.10.1_TBD</t>
+  </si>
+  <si>
+    <t>8_Gap Analysis</t>
+  </si>
+  <si>
+    <t>8.1_Governance Gaps</t>
+  </si>
+  <si>
+    <t>8.1.1_TBD</t>
+  </si>
+  <si>
+    <t>8.2_Technology Gaps</t>
+  </si>
+  <si>
+    <t>8.2.1_TBD</t>
+  </si>
+  <si>
+    <t>8.3_Organizational Gaps</t>
+  </si>
+  <si>
+    <t>8.3.1_TBD</t>
+  </si>
+  <si>
+    <t>8.4_Metadata Gaps</t>
+  </si>
+  <si>
+    <t>8.4.1_TBD</t>
+  </si>
+  <si>
+    <t>8.5_Lineage Gaps</t>
+  </si>
+  <si>
+    <t>8.5.1_TBD</t>
+  </si>
+  <si>
+    <t>8.6_Data Quality Gaps</t>
+  </si>
+  <si>
+    <t>8.6.1_TBD</t>
+  </si>
+  <si>
+    <t>9_Target State Governance Framework</t>
+  </si>
+  <si>
+    <t>9.1_Governance Vision</t>
+  </si>
+  <si>
+    <t>9.1.1_TBD</t>
+  </si>
+  <si>
+    <t>9.2_Governance Council Design</t>
+  </si>
+  <si>
+    <t>9.2.1_TBD</t>
+  </si>
+  <si>
+    <t>9.3_Stewardship Model Design</t>
+  </si>
+  <si>
+    <t>9.3.1_TBD</t>
+  </si>
+  <si>
+    <t>9.4_RACI Development</t>
+  </si>
+  <si>
+    <t>9.4.1_TBD</t>
+  </si>
+  <si>
+    <t>9.5_Escalation Framework</t>
+  </si>
+  <si>
+    <t>9.5.1_TBD</t>
+  </si>
+  <si>
+    <t>9.6_Decision Rights Framework</t>
+  </si>
+  <si>
+    <t>9.6.1_TBD</t>
+  </si>
+  <si>
+    <t>10_Target State Data Architecture</t>
+  </si>
+  <si>
+    <t>10.1_Enterprise Domain Model</t>
+  </si>
+  <si>
+    <t>10.1.1_TBD</t>
+  </si>
+  <si>
+    <t>10.2_Governance Architecture</t>
+  </si>
+  <si>
+    <t>10.2.1_Unity Catalog Architecture</t>
+  </si>
+  <si>
+    <t>10.2.2_Metadata Architecture</t>
+  </si>
+  <si>
+    <t>10.2.3_DQ Architecture</t>
+  </si>
+  <si>
+    <t>10.2.4_Lineage Architecture</t>
+  </si>
+  <si>
+    <t>10.2.5_Security Architecture</t>
+  </si>
+  <si>
+    <t>10.3_Medallion Architecture Design</t>
+  </si>
+  <si>
+    <t>10.3.1_TBD</t>
   </si>
 </sst>
 </file>
@@ -1146,6 +1486,82 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3F4835-2861-4670-8A6E-07666D3AF057}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="40.08984375" customWidth="1"/>
+    <col min="2" max="2" width="23.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="C2" s="15"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="B3" s="13">
+        <v>0.25</v>
+      </c>
+      <c r="C3" s="16"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="B4" s="13">
+        <v>0.18</v>
+      </c>
+      <c r="C4" s="17"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="B5" s="13">
+        <v>0.05</v>
+      </c>
+      <c r="C5" s="17"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="13">
+        <v>0</v>
+      </c>
+      <c r="C6" s="17"/>
+    </row>
+    <row r="7" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="14">
+        <v>0.25</v>
+      </c>
+      <c r="C7" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0D063CA-B174-49B5-AEB3-A144F54707FA}">
   <dimension ref="A1:E100"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1276,7 +1692,7 @@
       <c r="E8" s="11"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="7">
+      <c r="A9" s="6">
         <v>2.1</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -1351,7 +1767,7 @@
       <c r="E13" s="10"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="7">
+      <c r="A14" s="6">
         <v>2.2000000000000002</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -1471,7 +1887,7 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="7">
+      <c r="A22" s="6">
         <v>2.2999999999999998</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -1546,7 +1962,7 @@
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="7">
+      <c r="A27" s="6">
         <v>3.1</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -1591,7 +2007,7 @@
       <c r="E29" s="10"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="7">
+      <c r="A30" s="6">
         <v>3.2</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -1636,7 +2052,7 @@
       <c r="E32" s="10"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="7">
+      <c r="A33" s="6">
         <v>4.0999999999999996</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -1726,7 +2142,7 @@
       <c r="E38" s="10"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="7">
+      <c r="A39" s="6">
         <v>5.0999999999999996</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -1816,7 +2232,7 @@
       <c r="E44" s="10"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="7">
+      <c r="A45" s="6">
         <v>5.2</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -1891,7 +2307,7 @@
       <c r="E49" s="10"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="7">
+      <c r="A50" s="6">
         <v>6.1</v>
       </c>
       <c r="B50" s="4" t="s">
@@ -1966,7 +2382,7 @@
       <c r="E54" s="10"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="7">
+      <c r="A55" s="6">
         <v>6.2</v>
       </c>
       <c r="B55" s="4" t="s">
@@ -2660,76 +3076,752 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3F4835-2861-4670-8A6E-07666D3AF057}">
-  <dimension ref="A1:C7"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EB43DF2-4C0F-40A1-9B3F-C9F1ED4765B4}">
+  <dimension ref="A1:C67"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.08984375" customWidth="1"/>
-    <col min="2" max="2" width="23.7265625" customWidth="1"/>
+    <col min="1" max="1" width="42.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>210</v>
+      <c r="A1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="C2" s="15"/>
+      <c r="A2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="B3" s="13">
-        <v>0.25</v>
-      </c>
-      <c r="C3" s="16"/>
+      <c r="A3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="B4" s="13">
-        <v>0.18</v>
-      </c>
-      <c r="C4" s="17"/>
+      <c r="A4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="B5" s="13">
-        <v>0.05</v>
-      </c>
-      <c r="C5" s="17"/>
+      <c r="A5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="B6" s="13">
-        <v>0</v>
-      </c>
-      <c r="C6" s="17"/>
-    </row>
-    <row r="7" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B7" s="14">
-        <v>0.25</v>
-      </c>
-      <c r="C7" s="16"/>
+      <c r="A6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>223</v>
+      </c>
+      <c r="B7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>223</v>
+      </c>
+      <c r="B9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C9" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>223</v>
+      </c>
+      <c r="B10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>223</v>
+      </c>
+      <c r="B11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C11" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>223</v>
+      </c>
+      <c r="B12" t="s">
+        <v>229</v>
+      </c>
+      <c r="C12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>223</v>
+      </c>
+      <c r="B13" t="s">
+        <v>229</v>
+      </c>
+      <c r="C13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" t="s">
+        <v>229</v>
+      </c>
+      <c r="C14" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>223</v>
+      </c>
+      <c r="B15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C15" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>223</v>
+      </c>
+      <c r="B16" t="s">
+        <v>237</v>
+      </c>
+      <c r="C16" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>223</v>
+      </c>
+      <c r="B17" t="s">
+        <v>237</v>
+      </c>
+      <c r="C17" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>223</v>
+      </c>
+      <c r="B18" t="s">
+        <v>237</v>
+      </c>
+      <c r="C18" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>241</v>
+      </c>
+      <c r="B19" t="s">
+        <v>242</v>
+      </c>
+      <c r="C19" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>241</v>
+      </c>
+      <c r="B20" t="s">
+        <v>242</v>
+      </c>
+      <c r="C20" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>241</v>
+      </c>
+      <c r="B21" t="s">
+        <v>245</v>
+      </c>
+      <c r="C21" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>247</v>
+      </c>
+      <c r="B22" t="s">
+        <v>248</v>
+      </c>
+      <c r="C22" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>247</v>
+      </c>
+      <c r="B23" t="s">
+        <v>248</v>
+      </c>
+      <c r="C23" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>247</v>
+      </c>
+      <c r="B24" t="s">
+        <v>248</v>
+      </c>
+      <c r="C24" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>247</v>
+      </c>
+      <c r="B25" t="s">
+        <v>248</v>
+      </c>
+      <c r="C25" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>253</v>
+      </c>
+      <c r="B26" t="s">
+        <v>254</v>
+      </c>
+      <c r="C26" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>253</v>
+      </c>
+      <c r="B27" t="s">
+        <v>254</v>
+      </c>
+      <c r="C27" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>253</v>
+      </c>
+      <c r="B28" t="s">
+        <v>254</v>
+      </c>
+      <c r="C28" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>253</v>
+      </c>
+      <c r="B29" t="s">
+        <v>254</v>
+      </c>
+      <c r="C29" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>253</v>
+      </c>
+      <c r="B30" t="s">
+        <v>254</v>
+      </c>
+      <c r="C30" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>253</v>
+      </c>
+      <c r="B31" t="s">
+        <v>260</v>
+      </c>
+      <c r="C31" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>253</v>
+      </c>
+      <c r="B32" t="s">
+        <v>260</v>
+      </c>
+      <c r="C32" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>253</v>
+      </c>
+      <c r="B33" t="s">
+        <v>260</v>
+      </c>
+      <c r="C33" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>264</v>
+      </c>
+      <c r="B34" t="s">
+        <v>265</v>
+      </c>
+      <c r="C34" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>264</v>
+      </c>
+      <c r="B35" t="s">
+        <v>265</v>
+      </c>
+      <c r="C35" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>264</v>
+      </c>
+      <c r="B36" t="s">
+        <v>265</v>
+      </c>
+      <c r="C36" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>264</v>
+      </c>
+      <c r="B37" t="s">
+        <v>265</v>
+      </c>
+      <c r="C37" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>264</v>
+      </c>
+      <c r="B38" t="s">
+        <v>270</v>
+      </c>
+      <c r="C38" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>272</v>
+      </c>
+      <c r="B39" t="s">
+        <v>273</v>
+      </c>
+      <c r="C39" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>272</v>
+      </c>
+      <c r="B40" t="s">
+        <v>275</v>
+      </c>
+      <c r="C40" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>272</v>
+      </c>
+      <c r="B41" t="s">
+        <v>277</v>
+      </c>
+      <c r="C41" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>272</v>
+      </c>
+      <c r="B42" t="s">
+        <v>279</v>
+      </c>
+      <c r="C42" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>272</v>
+      </c>
+      <c r="B43" t="s">
+        <v>281</v>
+      </c>
+      <c r="C43" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>272</v>
+      </c>
+      <c r="B44" t="s">
+        <v>283</v>
+      </c>
+      <c r="C44" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>272</v>
+      </c>
+      <c r="B45" t="s">
+        <v>285</v>
+      </c>
+      <c r="C45" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>272</v>
+      </c>
+      <c r="B46" t="s">
+        <v>287</v>
+      </c>
+      <c r="C46" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>272</v>
+      </c>
+      <c r="B47" t="s">
+        <v>289</v>
+      </c>
+      <c r="C47" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>272</v>
+      </c>
+      <c r="B48" t="s">
+        <v>291</v>
+      </c>
+      <c r="C48" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>293</v>
+      </c>
+      <c r="B49" t="s">
+        <v>294</v>
+      </c>
+      <c r="C49" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>293</v>
+      </c>
+      <c r="B50" t="s">
+        <v>296</v>
+      </c>
+      <c r="C50" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>293</v>
+      </c>
+      <c r="B51" t="s">
+        <v>298</v>
+      </c>
+      <c r="C51" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>293</v>
+      </c>
+      <c r="B52" t="s">
+        <v>300</v>
+      </c>
+      <c r="C52" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>293</v>
+      </c>
+      <c r="B53" t="s">
+        <v>302</v>
+      </c>
+      <c r="C53" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>293</v>
+      </c>
+      <c r="B54" t="s">
+        <v>304</v>
+      </c>
+      <c r="C54" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>306</v>
+      </c>
+      <c r="B55" t="s">
+        <v>307</v>
+      </c>
+      <c r="C55" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>306</v>
+      </c>
+      <c r="B56" t="s">
+        <v>309</v>
+      </c>
+      <c r="C56" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>306</v>
+      </c>
+      <c r="B57" t="s">
+        <v>311</v>
+      </c>
+      <c r="C57" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>306</v>
+      </c>
+      <c r="B58" t="s">
+        <v>313</v>
+      </c>
+      <c r="C58" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>306</v>
+      </c>
+      <c r="B59" t="s">
+        <v>315</v>
+      </c>
+      <c r="C59" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>306</v>
+      </c>
+      <c r="B60" t="s">
+        <v>317</v>
+      </c>
+      <c r="C60" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>319</v>
+      </c>
+      <c r="B61" t="s">
+        <v>320</v>
+      </c>
+      <c r="C61" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>319</v>
+      </c>
+      <c r="B62" t="s">
+        <v>322</v>
+      </c>
+      <c r="C62" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>319</v>
+      </c>
+      <c r="B63" t="s">
+        <v>322</v>
+      </c>
+      <c r="C63" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>319</v>
+      </c>
+      <c r="B64" t="s">
+        <v>322</v>
+      </c>
+      <c r="C64" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>319</v>
+      </c>
+      <c r="B65" t="s">
+        <v>322</v>
+      </c>
+      <c r="C65" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>319</v>
+      </c>
+      <c r="B66" t="s">
+        <v>322</v>
+      </c>
+      <c r="C66" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>319</v>
+      </c>
+      <c r="B67" t="s">
+        <v>328</v>
+      </c>
+      <c r="C67" t="s">
+        <v>329</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/wiki/di/BradescoRSM.xlsx
+++ b/wiki/di/BradescoRSM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enrique.escobar\Disk_X\bbank_dw\wiki\di\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C5CD1F-5980-48BB-8583-5B891EC38BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2AAC71-877F-4FDD-AAE3-E08FDDD065B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" activeTab="2" xr2:uid="{2E3D8C18-206E-4258-BE0B-F3DC62B20D77}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{2E3D8C18-206E-4258-BE0B-F3DC62B20D77}"/>
   </bookViews>
   <sheets>
     <sheet name="Metrics" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="333">
   <si>
     <t>WBS ID</t>
   </si>
@@ -1028,13 +1028,22 @@
   </si>
   <si>
     <t>10.3.1_TBD</t>
+  </si>
+  <si>
+    <t>80+</t>
+  </si>
+  <si>
+    <t>0+</t>
+  </si>
+  <si>
+    <t>20+</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1043,6 +1052,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -1108,50 +1125,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1487,14 +1505,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3F4835-2861-4670-8A6E-07666D3AF057}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40.08984375" customWidth="1"/>
     <col min="2" max="2" width="23.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>209</v>
       </c>
@@ -1502,7 +1520,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
         <v>211</v>
       </c>
@@ -1510,8 +1528,11 @@
         <v>0.8</v>
       </c>
       <c r="C2" s="15"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="18" t="s">
         <v>212</v>
       </c>
@@ -1519,8 +1540,11 @@
         <v>0.25</v>
       </c>
       <c r="C3" s="16"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
         <v>213</v>
       </c>
@@ -1528,8 +1552,11 @@
         <v>0.18</v>
       </c>
       <c r="C4" s="17"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="18" t="s">
         <v>214</v>
       </c>
@@ -1537,8 +1564,11 @@
         <v>0.05</v>
       </c>
       <c r="C5" s="17"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D5" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
         <v>215</v>
       </c>
@@ -1546,8 +1576,11 @@
         <v>0</v>
       </c>
       <c r="C6" s="17"/>
-    </row>
-    <row r="7" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>216</v>
       </c>
@@ -1555,6 +1588,9 @@
         <v>0.25</v>
       </c>
       <c r="C7" s="16"/>
+      <c r="D7" t="s">
+        <v>332</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3087,10 +3123,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="19" t="s">
         <v>218</v>
       </c>
       <c r="C1" t="s">
@@ -3098,10 +3134,10 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="19" t="s">
         <v>218</v>
       </c>
       <c r="C2" t="s">
@@ -3109,10 +3145,10 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="19" t="s">
         <v>218</v>
       </c>
       <c r="C3" t="s">
@@ -3120,10 +3156,10 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="19" t="s">
         <v>218</v>
       </c>
       <c r="C4" t="s">
@@ -3131,10 +3167,10 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="19" t="s">
         <v>224</v>
       </c>
       <c r="C5" t="s">
@@ -3142,10 +3178,10 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="19" t="s">
         <v>224</v>
       </c>
       <c r="C6" t="s">
@@ -3153,10 +3189,10 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="19" t="s">
         <v>224</v>
       </c>
       <c r="C7" t="s">
@@ -3164,10 +3200,10 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="A8" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="19" t="s">
         <v>224</v>
       </c>
       <c r="C8" t="s">
@@ -3175,10 +3211,10 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="A9" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="19" t="s">
         <v>229</v>
       </c>
       <c r="C9" t="s">
@@ -3186,10 +3222,10 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="A10" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="19" t="s">
         <v>229</v>
       </c>
       <c r="C10" t="s">
@@ -3197,10 +3233,10 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="A11" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="19" t="s">
         <v>229</v>
       </c>
       <c r="C11" t="s">
@@ -3208,10 +3244,10 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="A12" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="19" t="s">
         <v>229</v>
       </c>
       <c r="C12" t="s">
@@ -3219,10 +3255,10 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="A13" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="19" t="s">
         <v>229</v>
       </c>
       <c r="C13" t="s">
@@ -3230,10 +3266,10 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="A14" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="19" t="s">
         <v>229</v>
       </c>
       <c r="C14" t="s">
@@ -3241,10 +3277,10 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="A15" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="19" t="s">
         <v>229</v>
       </c>
       <c r="C15" t="s">
@@ -3252,10 +3288,10 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="A16" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="19" t="s">
         <v>237</v>
       </c>
       <c r="C16" t="s">
@@ -3263,10 +3299,10 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="A17" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="19" t="s">
         <v>237</v>
       </c>
       <c r="C17" t="s">
@@ -3274,10 +3310,10 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="A18" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="19" t="s">
         <v>237</v>
       </c>
       <c r="C18" t="s">
@@ -3285,10 +3321,10 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="A19" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="19" t="s">
         <v>242</v>
       </c>
       <c r="C19" t="s">
@@ -3296,10 +3332,10 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="A20" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="19" t="s">
         <v>242</v>
       </c>
       <c r="C20" t="s">
@@ -3307,10 +3343,10 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="A21" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="19" t="s">
         <v>245</v>
       </c>
       <c r="C21" t="s">
@@ -3318,10 +3354,10 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="A22" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="19" t="s">
         <v>248</v>
       </c>
       <c r="C22" t="s">
@@ -3329,10 +3365,10 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="A23" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="19" t="s">
         <v>248</v>
       </c>
       <c r="C23" t="s">
@@ -3340,10 +3376,10 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="A24" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="19" t="s">
         <v>248</v>
       </c>
       <c r="C24" t="s">
@@ -3351,10 +3387,10 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="A25" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="19" t="s">
         <v>248</v>
       </c>
       <c r="C25" t="s">
@@ -3362,10 +3398,10 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+      <c r="A26" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="19" t="s">
         <v>254</v>
       </c>
       <c r="C26" t="s">
@@ -3373,10 +3409,10 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="A27" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="19" t="s">
         <v>254</v>
       </c>
       <c r="C27" t="s">
@@ -3384,10 +3420,10 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="A28" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="19" t="s">
         <v>254</v>
       </c>
       <c r="C28" t="s">
@@ -3395,10 +3431,10 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="A29" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="19" t="s">
         <v>254</v>
       </c>
       <c r="C29" t="s">
@@ -3406,10 +3442,10 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="A30" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="19" t="s">
         <v>254</v>
       </c>
       <c r="C30" t="s">
@@ -3417,10 +3453,10 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="A31" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="19" t="s">
         <v>260</v>
       </c>
       <c r="C31" t="s">
@@ -3428,10 +3464,10 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="A32" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="19" t="s">
         <v>260</v>
       </c>
       <c r="C32" t="s">
@@ -3439,10 +3475,10 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="A33" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="19" t="s">
         <v>260</v>
       </c>
       <c r="C33" t="s">
@@ -3450,10 +3486,10 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="A34" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="19" t="s">
         <v>265</v>
       </c>
       <c r="C34" t="s">
@@ -3461,10 +3497,10 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="A35" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="19" t="s">
         <v>265</v>
       </c>
       <c r="C35" t="s">
@@ -3472,10 +3508,10 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+      <c r="A36" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="19" t="s">
         <v>265</v>
       </c>
       <c r="C36" t="s">
@@ -3483,10 +3519,10 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+      <c r="A37" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="19" t="s">
         <v>265</v>
       </c>
       <c r="C37" t="s">
@@ -3494,10 +3530,10 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+      <c r="A38" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="19" t="s">
         <v>270</v>
       </c>
       <c r="C38" t="s">
